--- a/stories/arbres/TREE-FAM-006.xlsx
+++ b/stories/arbres/TREE-FAM-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est à la maison. Un verre a glissé. Tom a un nœud au ventre. Papa est là. Papa dit : tu peux raconter. On le dit à papa ou maman. Tom respire.</t>
+          <t>Tom est à la maison. Un verre a glissé. Tom a un nœud au ventre. Papa est là. Tu peux raconter. On le dit à papa ou maman. Tom respire.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est à la maison. Un verre a glissé. Tom a un nœud au ventre. Papa est là.
+papa|Tu peux raconter. On le dit à papa ou maman.
+narrateur|Tom respire.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le salon, la cuisine, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le salon. Le tapis est doux. papa est tout près. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Tom a retenu. Tom raconte. Il le dit à papa ou maman. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le verre. L'eau a fait un bruit. papa montre lentement. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. Papa est près. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. La lumière est douce. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le coussin. Le coussin est au sol. papa montre lentement. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4116,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. La lumière est douce. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4283,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4450,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4617,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4784,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. La chaise est vide. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4951,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5118,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le crayon. Le crayon a roulé. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5313,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5480,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5647,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5814,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. La chaise est vide. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5981,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5851,7 +6010,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint la sœur. Le bol est chaud. Tom dit : c'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
+          <t>Tom rejoint la sœur. Le bol est chaud. C'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5989,6 +6148,13 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. Le bol est chaud.
+enfant-m|C'est moi.
+narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6317,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6484,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la cuisine. Il y a des miettes. papa est tout près. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6491,6 +6667,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6515,7 +6696,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tom respire. Tom raconte. Il le dit à papa ou maman. papa dit : je suis là.</t>
+          <t>Tom respire. Tom raconte. Il le dit à papa ou maman. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6657,6 +6838,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Tom respire. Tom raconte. Il le dit à papa ou maman.
+papa|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7030,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7197,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le verre. Papa est près. papa montre lentement. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7392,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7357,6 +7559,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. La lumière est douce. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7726,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7893,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. Un chat miaule. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8060,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8227,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8394,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8561,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le coussin. La lumière est douce. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8756,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8681,6 +8923,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. Un chat miaule. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9090,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9257,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9424,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9591,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. Le bol est chaud. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9758,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9515,7 +9787,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le crayon. Un chat miaule. papa montre lentement. Tom dit : c'est moi. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+          <t>Tom a choisi le crayon. Un chat miaule. papa montre lentement. C'est moi. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9653,6 +9925,13 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le crayon. Un chat miaule. papa montre lentement.
+enfant-m|C'est moi.
+narrateur|Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10122,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10005,6 +10289,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10456,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10329,6 +10623,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. Le bol est chaud. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10790,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10515,7 +10819,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint la sœur. On entend un oiseau. Tom dit : c'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
+          <t>Tom rejoint la sœur. On entend un oiseau. C'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10653,6 +10957,13 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. On entend un oiseau.
+enfant-m|C'est moi.
+narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11126,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10977,6 +11293,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la chambre. La couverture est tiède. papa est tout près. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11474,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11647,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Tom raconte. Il le dit à papa ou maman. Tom donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11838,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +12005,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le verre. La chaise est vide. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12200,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12021,6 +12367,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. Un chat miaule. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12534,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12701,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. La chaise est vide. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12868,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13035,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13202,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12855,7 +13231,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le coussin. Le bol est chaud. papa montre lentement. Tom dit : c'est moi. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+          <t>Tom a choisi le coussin. Le bol est chaud. papa montre lentement. C'est moi. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12993,6 +13369,13 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le coussin. Le bol est chaud. papa montre lentement.
+enfant-m|C'est moi.
+narrateur|Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13566,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13345,6 +13733,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. La chaise est vide. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13900,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13669,6 +14067,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14234,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13993,6 +14401,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. On entend un oiseau. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14568,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14735,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le crayon. On entend un oiseau. papa montre lentement. Tom raconte. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14507,6 +14930,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14669,6 +15097,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint maman. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15264,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14993,6 +15431,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint papa. On entend un oiseau. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15598,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15179,7 +15627,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint la sœur. Le tapis est doux. Tom dit : c'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
+          <t>Tom rejoint la sœur. Le tapis est doux. C'est moi. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15317,6 +15765,13 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint la sœur. Le tapis est doux.
+enfant-m|C'est moi.
+narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15934,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +15957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15514,6 +15974,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-006.xlsx
+++ b/stories/arbres/TREE-FAM-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Tom respire.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le salon, la cuisine, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|Tom va vers le salon. Le tapis est doux. papa est tout près. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Tom a retenu. Tom raconte. Il le dit à papa ou maman. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Tom a choisi le verre. L'eau a fait un bruit. papa montre lentement. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Tom rejoint maman. Papa est près. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Tom rejoint papa. La lumière est douce. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Tom rejoint la sœur. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le verre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|Tom a choisi le coussin. Le coussin est au sol. papa montre lentement. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3974,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4121,6 +4142,7 @@
           <t>narrateur|Tom rejoint maman. La lumière est douce. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4288,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4478,7 @@
           <t>narrateur|Tom rejoint papa. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4789,6 +4814,7 @@
           <t>narrateur|Tom rejoint la sœur. La chaise est vide. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4956,6 +4982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5123,6 +5150,7 @@
           <t>narrateur|Tom a choisi le crayon. Le crayon a roulé. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5318,6 +5346,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5485,6 +5514,7 @@
           <t>narrateur|Tom rejoint maman. Un chat miaule. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5652,6 +5682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5819,6 +5850,7 @@
           <t>narrateur|Tom rejoint papa. La chaise est vide. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5986,6 +6018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6155,6 +6188,7 @@
 narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. le salon, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6322,6 +6356,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6489,6 +6524,7 @@
           <t>narrateur|Tom va vers la cuisine. Il y a des miettes. papa est tout près. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6672,6 +6708,7 @@
           <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6844,6 +6881,7 @@
 papa|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7035,6 +7073,7 @@
           <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7202,6 +7241,7 @@
           <t>narrateur|Tom a choisi le verre. Papa est près. papa montre lentement. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7397,6 +7437,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7564,6 +7605,7 @@
           <t>narrateur|Tom rejoint maman. La lumière est douce. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7731,6 +7773,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7898,6 +7941,7 @@
           <t>narrateur|Tom rejoint papa. Un chat miaule. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8065,6 +8109,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8232,6 +8277,7 @@
           <t>narrateur|Tom rejoint la sœur. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le verre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8399,6 +8445,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8566,6 +8613,7 @@
           <t>narrateur|Tom a choisi le coussin. La lumière est douce. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8761,6 +8809,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8928,6 +8977,7 @@
           <t>narrateur|Tom rejoint maman. Un chat miaule. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9095,6 +9145,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9262,6 +9313,7 @@
           <t>narrateur|Tom rejoint papa. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9429,6 +9481,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9596,6 +9649,7 @@
           <t>narrateur|Tom rejoint la sœur. Le bol est chaud. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9763,6 +9817,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9932,6 +9987,7 @@
 narrateur|Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10127,6 +10183,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10294,6 +10351,7 @@
           <t>narrateur|Tom rejoint maman. La chaise est vide. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10461,6 +10519,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10628,6 +10687,7 @@
           <t>narrateur|Tom rejoint papa. Le bol est chaud. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10795,6 +10855,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10964,6 +11025,7 @@
 narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. la cuisine, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11131,6 +11193,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11298,6 +11361,7 @@
           <t>narrateur|Tom va vers la chambre. La couverture est tiède. papa est tout près. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11481,6 +11545,7 @@
           <t>narrateur|Une bêtise est arrivée. Que fait Tom ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11652,6 +11717,7 @@
           <t>narrateur|C'est juste. Tom raconte. Il le dit à papa ou maman. Tom donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11843,6 +11909,7 @@
           <t>narrateur|On peut prendre le verre, le coussin, ou le crayon.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12010,6 +12077,7 @@
           <t>narrateur|Tom a choisi le verre. La chaise est vide. papa montre lentement. Tom prend la main. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12205,6 +12273,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12372,6 +12441,7 @@
           <t>narrateur|Tom rejoint maman. Un chat miaule. Tom raconte. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12539,6 +12609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12706,6 +12777,7 @@
           <t>narrateur|Tom rejoint papa. La chaise est vide. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12873,6 +12945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13040,6 +13113,7 @@
           <t>narrateur|Tom rejoint la sœur. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le verre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13207,6 +13281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13376,6 +13451,7 @@
 narrateur|Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13571,6 +13647,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13738,6 +13815,7 @@
           <t>narrateur|Tom rejoint maman. La chaise est vide. Tom dit ce qui s'est passé. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13905,6 +13983,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14072,6 +14151,7 @@
           <t>narrateur|Tom rejoint papa. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14239,6 +14319,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14406,6 +14487,7 @@
           <t>narrateur|Tom rejoint la sœur. On entend un oiseau. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le coussin.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14573,6 +14655,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14740,6 +14823,7 @@
           <t>narrateur|Tom a choisi le crayon. On entend un oiseau. papa montre lentement. Tom raconte. Tom raconte. Il le dit à papa ou maman. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14935,6 +15019,7 @@
           <t>narrateur|On peut prendre maman, papa, ou la sœur.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15102,6 +15187,7 @@
           <t>narrateur|Tom rejoint maman. Le bol est chaud. Tom va vers papa. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15269,6 +15355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15436,6 +15523,7 @@
           <t>narrateur|Tom rejoint papa. On entend un oiseau. Tom prend la main. Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15603,6 +15691,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15772,6 +15861,7 @@
 narrateur|Tom raconte. Il le dit à papa ou maman. papa dit merci. la chambre, puis le crayon.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15939,6 +16029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15957,7 +16048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15981,6 +16072,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15995,7 +16100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16182,6 +16287,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
